--- a/recruiter_forms/004_job_seekers_application_form--recruiter_forms.xlsx
+++ b/recruiter_forms/004_job_seekers_application_form--recruiter_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>job_type</t>
+          <t>job_type_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Job Type</t>
+          <t>Job Type 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>job_description_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Job Description</t>
+          <t>Job Description 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>job_status</t>
+          <t>job_status_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Job Status</t>
+          <t>Job Status 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1078,9 +1078,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'id1',_'label':_'skill_1',_'value':_'skill1'}</t>
+          <t>skill_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 'id1', 'label': 'Skill 1', 'value': 'skill1'}</t>
+          <t>Skill 1</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'id2',_'label':_'skill_2',_'value':_'skill2'}</t>
+          <t>skill_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 'id2', 'label': 'Skill 2', 'value': 'skill2'}</t>
+          <t>Skill 2</t>
         </is>
       </c>
     </row>
@@ -1142,63 +1142,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'id3',_'label':_'skill_3',_'value':_'skill3'}</t>
+          <t>skill_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 'id3', 'label': 'Skill 3', 'value': 'skill3'}</t>
+          <t>Skill 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_type_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'id1',_'label':_'type_1',_'value':_'value1'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'id1', 'label': 'Type 1', 'value': 'value1'}</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_type_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'id2',_'label':_'type_2',_'value':_'value2'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'id2', 'label': 'Type 2', 'value': 'value2'}</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_type_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'id3',_'label':_'type_3',_'value':_'value3'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 'id3', 'label': 'Type 3', 'value': 'value3'}</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
